--- a/artfynd/A 32944-2024 artfynd.xlsx
+++ b/artfynd/A 32944-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>94949428</v>
+        <v>94939396</v>
       </c>
       <c r="B2" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519932.0455569217</v>
+        <v>519932</v>
       </c>
       <c r="R2" t="n">
-        <v>6313726.672833056</v>
+        <v>6313727</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2016-06-20</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2016-10-15</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -804,12 +789,7 @@
         <v>94949408</v>
       </c>
       <c r="B3" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -841,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519906.4555216707</v>
+        <v>519906</v>
       </c>
       <c r="R3" t="n">
-        <v>6313709.651656915</v>
+        <v>6313709</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,19 +854,9 @@
           <t>2016-06-20</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2016-10-15</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -927,15 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>94939396</v>
+        <v>94949428</v>
       </c>
       <c r="B4" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -943,21 +908,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -967,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519932.0455569217</v>
+        <v>519932</v>
       </c>
       <c r="R4" t="n">
-        <v>6313726.672833056</v>
+        <v>6313727</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1000,19 +965,9 @@
           <t>2016-06-20</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2016-10-15</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
